--- a/results/tables/17_final_CR2.xlsx
+++ b/results/tables/17_final_CR2.xlsx
@@ -12,21 +12,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t xml:space="preserve">Variable</t>
   </si>
   <si>
-    <t xml:space="preserve">Coef</t>
-  </si>
-  <si>
     <t xml:space="preserve">beta</t>
   </si>
   <si>
     <t xml:space="preserve">SE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">null_value</t>
   </si>
   <si>
     <t xml:space="preserve">tstat</t>
@@ -395,115 +389,85 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.0171577292272653</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0179142524069589</v>
+        <v>0.0123895461213593</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0188522451988809</v>
+        <v>-1.3848553497602</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>2.44385191482427</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.950245035430702</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.00000059707287</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.516237947843076</v>
+        <v>0.278965500316458</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.000623820651082472</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000627041351773554</v>
+        <v>0.000265016532654134</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00223133321899561</v>
+        <v>2.3538933395397</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3.42970985247456</v>
       </c>
       <c r="F3" t="n">
-        <v>0.281016455290261</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.00000256856122</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.825597276671413</v>
+        <v>0.0890340124124235</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.0557642436252803</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0558541192756409</v>
+        <v>0.0103224549132228</v>
       </c>
       <c r="D4" t="n">
-        <v>0.256391893504357</v>
+        <v>-5.40222690184367</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>2.67859783257233</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.217846666336554</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.00000249931545</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.863447883405257</v>
+        <v>0.0165513486876205</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-0.0000680469738216604</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.000099700139084651</v>
+        <v>0.000338719713224403</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000855343668188888</v>
+        <v>-0.200894636966639</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2.56555360583706</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.116561497784577</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.00000170598225</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.926127973638352</v>
+        <v>0.855624928094917</v>
       </c>
     </row>
   </sheetData>
